--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104617_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104617_W18.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9668</v>
+        <v>7.0972</v>
       </c>
       <c r="E2" t="n">
-        <v>9.895799999999999</v>
+        <v>8.922800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9289</v>
+        <v>-1.8256</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6667</v>
+        <v>6.6664</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7862</v>
+        <v>1.7973</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8805</v>
+        <v>4.869</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3665</v>
+        <v>6.3366</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5282</v>
+        <v>2.5166</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8382</v>
+        <v>3.8201</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3002</v>
+        <v>0.3297</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3513</v>
+        <v>0.4716</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8903</v>
+        <v>0.952</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.539</v>
+        <v>-0.4804</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6203</v>
+        <v>6.2256</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6697</v>
+        <v>4.0969</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9506</v>
+        <v>2.1286</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0075</v>
+        <v>3.9841</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4303</v>
+        <v>3.4041</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3801</v>
+        <v>3.3389</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4867</v>
+        <v>2.4565</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.0545</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4174</v>
+        <v>0.0556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2646</v>
+        <v>-0.11</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5895</v>
+        <v>5.1856</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3855</v>
+        <v>2.8941</v>
       </c>
       <c r="F4" t="n">
-        <v>2.204</v>
+        <v>2.2914</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2976</v>
+        <v>3.297</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1516</v>
+        <v>-0.1467</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4491</v>
+        <v>3.4438</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2301</v>
+        <v>2.2069</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3482</v>
+        <v>2.3383</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0674</v>
+        <v>1.0901</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.5228</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1553</v>
+        <v>0.6873</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2244</v>
+        <v>-0.1645</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5258</v>
+        <v>4.2445</v>
       </c>
       <c r="E5" t="n">
-        <v>6.126</v>
+        <v>2.2166</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6002</v>
+        <v>2.0278</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7434</v>
+        <v>3.7578</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9784</v>
+        <v>1.358</v>
       </c>
       <c r="I5" t="n">
-        <v>0.765</v>
+        <v>2.3998</v>
       </c>
       <c r="J5" t="n">
-        <v>3.315</v>
+        <v>3.1414</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5314</v>
+        <v>1.6892</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7837</v>
+        <v>1.4522</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5716</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.553</v>
+        <v>-0.3312</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>0.9476</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2853</v>
+        <v>0.1013</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3288</v>
+        <v>0.0556</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0436</v>
+        <v>0.0457</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8639</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4822</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0475</v>
+        <v>2.5759</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7616</v>
+        <v>4.3251</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2859</v>
+        <v>-1.7492</v>
       </c>
       <c r="G6" t="n">
-        <v>3.748</v>
+        <v>2.7438</v>
       </c>
       <c r="H6" t="n">
-        <v>1.349</v>
+        <v>1.9734</v>
       </c>
       <c r="I6" t="n">
-        <v>2.399</v>
+        <v>0.7704</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1524</v>
+        <v>3.2878</v>
       </c>
       <c r="K6" t="n">
-        <v>1.697</v>
+        <v>2.5059</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4554</v>
+        <v>0.782</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5956</v>
+        <v>-0.5441</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.348</v>
+        <v>-0.5325</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9436</v>
+        <v>-0.0116</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.3297</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4174</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3293</v>
+        <v>-0.2342</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1607</v>
+        <v>-1.8634</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.4733</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1555</v>
+        <v>2.4755</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0238</v>
+        <v>3.3607</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8683</v>
+        <v>-0.8852</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0969</v>
+        <v>0.1002</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6783</v>
+        <v>-1.6692</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7752</v>
+        <v>1.7694</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9595</v>
+        <v>0.9473</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8626</v>
+        <v>-0.8471</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3536</v>
+        <v>-0.0313</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.121</v>
+        <v>0.2345</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2326</v>
+        <v>-0.2658</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4544</v>
+        <v>1.5581</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1742</v>
+        <v>0.1568</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6286</v>
+        <v>1.4013</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.412</v>
+        <v>-0.4117</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8325</v>
+        <v>1.8378</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2444</v>
+        <v>-2.2495</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.293</v>
+        <v>-0.3122</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9914</v>
+        <v>1.9822</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1189</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8142</v>
+        <v>-0.7131</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1597</v>
+        <v>-0.0926</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.221</v>
+        <v>0.8143</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0019</v>
+        <v>0.3115</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2229</v>
+        <v>0.5029</v>
       </c>
       <c r="G9" t="n">
-        <v>0.975</v>
+        <v>0.964</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7015</v>
+        <v>-0.6899</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6764</v>
+        <v>1.654</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0184</v>
+        <v>1.9819</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8523</v>
+        <v>1.8235</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0434</v>
+        <v>-1.0179</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5933</v>
+        <v>-0.9919</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7071</v>
+        <v>-0.4596</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4092</v>
+        <v>-1.0314</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4373</v>
+        <v>-1.9959</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8465</v>
+        <v>0.9646</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5346</v>
+        <v>-0.5157</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6999</v>
+        <v>0.2381</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1653</v>
+        <v>-0.7537</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5625</v>
+        <v>-0.2582</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7864</v>
+        <v>0.3825</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2239</v>
+        <v>-0.6407</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9721</v>
+        <v>-0.2574</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9135</v>
+        <v>-0.1444</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0599</v>
+        <v>-0.7433</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0514</v>
+        <v>-0.5995</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.1438</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5226</v>
+        <v>-1.2351</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2148</v>
+        <v>0.6603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6922</v>
+        <v>-1.8954</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5221</v>
+        <v>-1.5279</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2322</v>
+        <v>-1.6948</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7543</v>
+        <v>0.1669</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2459</v>
+        <v>-0.5662</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3912</v>
+        <v>-0.7896</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6371</v>
+        <v>0.2234</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2762</v>
+        <v>-0.9617</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.159</v>
+        <v>-0.9052</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1172</v>
+        <v>-0.0565</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2273</v>
+        <v>0.1138</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>0.1857</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3926</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6176</v>
+        <v>-1.4029</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4871</v>
+        <v>-2.2637</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8696</v>
+        <v>0.8608</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3619</v>
+        <v>-0.3542</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3348</v>
+        <v>-1.33</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9729</v>
+        <v>0.9758</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0052</v>
+        <v>-1.0139</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1917</v>
+        <v>-1.2001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3899</v>
+        <v>-0.1868</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0421</v>
+        <v>-0.0752</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3322</v>
+        <v>-2.7984</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9397</v>
+        <v>-4.4873</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6075</v>
+        <v>1.6889</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1751</v>
+        <v>-1.1701</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3202</v>
+        <v>0.327</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4954</v>
+        <v>-1.4971</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9062</v>
+        <v>-1.918</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M13" t="n">
-        <v>0.731</v>
+        <v>0.7479</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0229</v>
+        <v>-0.4901</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.2929</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2577</v>
+        <v>-0.1972</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.6992</v>
+        <v>23.7089</v>
       </c>
       <c r="E14" t="n">
-        <v>18.482</v>
+        <v>18.1979</v>
       </c>
       <c r="F14" t="n">
-        <v>5.2174</v>
+        <v>5.5109</v>
       </c>
       <c r="G14" t="n">
-        <v>17.5294</v>
+        <v>17.5337</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5095</v>
+        <v>2.581</v>
       </c>
       <c r="I14" t="n">
-        <v>15.0196</v>
+        <v>14.9529</v>
       </c>
       <c r="J14" t="n">
-        <v>17.40920000000001</v>
+        <v>17.1723</v>
       </c>
       <c r="K14" t="n">
-        <v>7.0146</v>
+        <v>6.8993</v>
       </c>
       <c r="L14" t="n">
-        <v>10.3946</v>
+        <v>10.273</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1201</v>
+        <v>0.3613</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.505</v>
+        <v>-4.318499999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>4.6251</v>
+        <v>4.6799</v>
       </c>
       <c r="P14" t="n">
-        <v>6.804800000000001</v>
+        <v>6.8288</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.9393</v>
+        <v>-7.967300000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6636</v>
+        <v>-1.6718</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5595000000000009</v>
+        <v>0.5779000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2232</v>
+        <v>-2.2495</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0285</v>
+        <v>1.0181</v>
       </c>
       <c r="W14" t="n">
-        <v>8.452299999999999</v>
+        <v>8.415100000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.4239</v>
+        <v>-7.3971</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.034</v>
+        <v>4.1013</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5651</v>
+        <v>3.8078</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4688</v>
+        <v>0.2935</v>
       </c>
       <c r="G15" t="n">
-        <v>0.185</v>
+        <v>0.1789</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7016</v>
+        <v>1.6813</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5166</v>
+        <v>-1.5024</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7215</v>
+        <v>1.6793</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3959</v>
+        <v>2.3572</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5365</v>
+        <v>-1.5004</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8245</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8243</v>
+        <v>0.9013</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2461</v>
+        <v>0.543</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5782</v>
+        <v>0.3583</v>
       </c>
       <c r="V15" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8945</v>
+        <v>1.62</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1828</v>
+        <v>2.6212</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2883</v>
+        <v>-1.0012</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5995</v>
+        <v>2.6066</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1515</v>
+        <v>2.1458</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4479</v>
+        <v>0.4609</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2565</v>
+        <v>3.2348</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1445</v>
+        <v>3.1231</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.657</v>
+        <v>-0.6282</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O16" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8058</v>
+        <v>1.5294</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3288</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4769</v>
+        <v>0.7286</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4692</v>
+        <v>-0.4673</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5619</v>
+        <v>-1.5568</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5375</v>
+        <v>-0.1219</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0124</v>
+        <v>0.7539</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4749</v>
+        <v>-0.8759</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.602</v>
+        <v>-0.5921</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9726</v>
+        <v>-0.9709</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3706</v>
+        <v>0.3787</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5477</v>
+        <v>1.5255</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0204</v>
+        <v>0.0065</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5273</v>
+        <v>1.519</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1497</v>
+        <v>-2.1177</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6767</v>
+        <v>1.0058</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8257</v>
+        <v>0.5942</v>
       </c>
       <c r="U17" t="n">
-        <v>0.851</v>
+        <v>0.4116</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0804</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0804</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.157</v>
+        <v>-0.2959</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3859</v>
+        <v>0.189</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7711</v>
+        <v>-0.4848</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8982</v>
+        <v>-0.8873</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0555</v>
+        <v>-1.0453</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6575</v>
+        <v>0.6423</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7721</v>
+        <v>0.7617</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5557</v>
+        <v>-1.5296</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0716</v>
+        <v>-0.2312</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0434</v>
+        <v>-0.4533</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0281</v>
+        <v>0.2221</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5932</v>
+        <v>-1.4122</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5105</v>
+        <v>-0.3984</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0827</v>
+        <v>-1.0138</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.269</v>
+        <v>-1.2682</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6955</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9645</v>
+        <v>-1.9633</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2322</v>
+        <v>-0.2381</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0368</v>
+        <v>-1.0301</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5511</v>
+        <v>-0.3717</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3536</v>
+        <v>-1.4191</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0386</v>
+        <v>0.7317</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3922</v>
+        <v>-2.1508</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9027</v>
+        <v>-2.8948</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0534</v>
+        <v>-0.0545</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8494</v>
+        <v>-2.8403</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2193</v>
+        <v>-0.232</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5204</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6834</v>
+        <v>-2.6628</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1003</v>
+        <v>-2.0879</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8474</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6079</v>
+        <v>0.1019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2395</v>
+        <v>-0.0207</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1698</v>
+        <v>1.1669</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9083</v>
+        <v>-4.8828</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4976</v>
+        <v>-0.5543</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.4059</v>
+        <v>-4.3285</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6977</v>
+        <v>-5.7189</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0877</v>
+        <v>-3.1329</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6099</v>
+        <v>-2.586</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6367</v>
+        <v>-3.3287</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6367</v>
+        <v>-2.6727</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.656</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3344</v>
+        <v>-2.3902</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7245</v>
+        <v>-0.4603</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6099</v>
+        <v>-1.93</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4776</v>
+        <v>-0.1639</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0858</v>
+        <v>0.0507</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6082</v>
+        <v>-0.2146</v>
       </c>
       <c r="V21" t="n">
-        <v>-4.5956</v>
+        <v>0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2249</v>
+        <v>2.7237</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.3707</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.611</v>
+        <v>-5.5831</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7487</v>
+        <v>0.7645</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.8623</v>
+        <v>-6.3477</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.7094</v>
+        <v>-1.7078</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.1239</v>
+        <v>-0.1053</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5856</v>
+        <v>-1.6025</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.2929</v>
+        <v>0.613</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.6503</v>
+        <v>0.613</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6425</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4166</v>
+        <v>-2.3209</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4735</v>
+        <v>-0.7184</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9431</v>
+        <v>-1.6025</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9016</v>
+        <v>-0.1988</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1875</v>
+        <v>0.3807</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7141</v>
+        <v>-0.5794</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5463</v>
+        <v>-4.5871</v>
       </c>
       <c r="W22" t="n">
-        <v>2.7317</v>
+        <v>-0.2292</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RICHARDSON</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.247299999999999</v>
+        <v>-7.1518</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.6449</v>
+        <v>-6.3296</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6024</v>
+        <v>-0.8222</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.9058</v>
+        <v>-1.3282</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.939</v>
+        <v>-0.0429</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9667</v>
+        <v>-1.2853</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.5419</v>
+        <v>0.3185</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1828</v>
+        <v>1.2648</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3591</v>
+        <v>-0.9463</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3639</v>
+        <v>-1.6467</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7563</v>
+        <v>-1.3077</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6077</v>
+        <v>-0.3391</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-5.9184</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-7.0566</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.604</v>
+        <v>0.0174</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>0.4085</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0039</v>
+        <v>-0.391</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>J. RICHARDSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.2949</v>
+        <v>-7.7736</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2239</v>
+        <v>-7.0967</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0709</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.329</v>
+        <v>-5.9219</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0389</v>
+        <v>-2.9545</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2901</v>
+        <v>-2.9673</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3462</v>
+        <v>-4.5762</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2845</v>
+        <v>-2.2073</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9383</v>
+        <v>-2.3689</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6752</v>
+        <v>-1.3457</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3234</v>
+        <v>-0.7472</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3517</v>
+        <v>-0.5984</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.8976</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.0318</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1454</v>
+        <v>-0.1081</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5383</v>
+        <v>-0.0166</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.607</v>
+        <v>-0.0915</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-23.6993</v>
+        <v>-22.9191</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2174</v>
+        <v>-5.5109</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.4819</v>
+        <v>-17.4083</v>
       </c>
       <c r="G25" t="n">
-        <v>-17.5293</v>
+        <v>-17.5337</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.5096</v>
+        <v>-2.5809</v>
       </c>
       <c r="I25" t="n">
-        <v>-15.0198</v>
+        <v>-14.9528</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.120200000000001</v>
+        <v>-0.361600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5048</v>
+        <v>4.3183</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.625100000000001</v>
+        <v>-4.6798</v>
       </c>
       <c r="M25" t="n">
-        <v>-17.4092</v>
+        <v>-17.1723</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.014699999999999</v>
+        <v>-6.899400000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.3945</v>
+        <v>-10.273</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7442</v>
+        <v>-14.796</v>
       </c>
       <c r="R25" t="n">
-        <v>7.9392</v>
+        <v>7.967200000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>1.663300000000001</v>
+        <v>2.4614</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2232</v>
+        <v>2.2496</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5596999999999999</v>
+        <v>0.2121000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0285</v>
+        <v>-1.018000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>7.4239</v>
+        <v>7.3972</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.452300000000001</v>
+        <v>-8.415099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104617_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104617_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.3971</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.5568</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.0804</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104617_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.415099999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
